--- a/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,87 +447,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>all elements (name | isPartOf)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.6562</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B3" t="n">
         <v>0.7241</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.8023</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>mean semantic meaning</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0.7241</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8478</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.9545</v>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mean semantic meaning</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3182</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2415</v>
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pageNumber</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.24</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2576</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>isPartOf</t>
+          <t>pageNumber</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -538,15 +541,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>isPartOf</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>fixes</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -608,13 +626,13 @@
         <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.72</v>
+        <v>0.8182</v>
       </c>
       <c r="F2" t="n">
         <v>0.7826</v>
@@ -652,16 +670,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -717,23 +735,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>False Positives</t>
+          <t>Validated correct (name for units/patterns, isPartOf for connectors)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>False Negatives</t>
+          <t>False Positives</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -743,30 +761,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Element Precision</t>
+          <t>False Negatives</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6286</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Element Recall</t>
+          <t>Precision (all elements; units/patterns by name, connectors by isPartOf)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6111</v>
+        <v>0.6153999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Recall (all elements; units/patterns by name, connectors by isPartOf)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Match threshold (cosine)</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -836,7 +864,7 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
         <v>22</v>
@@ -851,7 +879,7 @@
         <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -864,22 +892,22 @@
         <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -892,22 +920,22 @@
         <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +948,22 @@
         <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -948,22 +976,22 @@
         <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -991,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1005,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,7 +1141,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1127,7 +1155,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.535</v>
+        <v>0.5289</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1149,11 +1177,15 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -1191,7 +1223,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1205,21 +1237,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5394</v>
+        <v>0.6022</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Prisma ORM</t>
+          <t>Prisma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Object-Relational Mapping tool for database interaction.</t>
+          <t>ORM tool used to manage database access.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1235,7 +1267,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -1273,7 +1305,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1287,7 +1319,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6592</v>
+        <v>0.6508</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1301,7 +1333,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>External service for cloud file storage.</t>
+          <t>External cloud storage service for files.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1309,11 +1341,15 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1351,81 +1387,73 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_AD04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6912</v>
+        <v>0.7157</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Google OAuth</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Authentication provider.</t>
+          <t>Establishes a one-to-many relationship where subjects notify observers of state changes, implemented via event listeners in components.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['AU_10']</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Use Google for user authentication</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>CF_M09_AU09</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_AD04</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1433,12 +1461,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_AD05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1447,11 +1475,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6988</v>
+        <v>0.7595</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>Singleton Pattern</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1461,25 +1489,25 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Establishes a one-to-many relationship where subjects notify observers of state changes, implemented via event listeners in components.</t>
+          <t>Ensures a class has only one instance and provides a global access point, used here to manage the PrismaClient instance.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Singleton</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1489,17 +1517,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_AD05</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1507,12 +1535,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1521,11 +1549,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7415</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monitoring Service</t>
+          <t>Email Service</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1535,7 +1563,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>External service for tracking and managing application errors.</t>
+          <t>External service for sending and managing emails.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1543,17 +1571,21 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1563,7 +1595,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1577,7 +1609,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1585,73 +1617,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7591</v>
+        <v>0.9391</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Singleton Pattern</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ensures a class has only one instance and provides a global access point, used here to manage the PrismaClient instance.</t>
+          <t>External service for user authentication via Google.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Singleton</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1659,77 +1699,73 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8524</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Email Service</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>External service for creating and sending emails.</t>
+          <t>The system is built as a collection of small, independent services (Security Service, System Service, Data Service) that communicate with each other and are managed as Docker containers.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>architecture based on microservices</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1737,12 +1773,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1751,49 +1787,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9326</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>External service for user authentication.</t>
+          <t>Containerization platform used to manage and run services.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41, 76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Each of these services is contained in a Docker container</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1807,7 +1843,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1815,17 +1851,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1833,55 +1869,63 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The system is built as a collection of small, independent services (Security Service, System Service, Data Service) that communicate with each other and are managed as Docker containers.</t>
+          <t>Error monitoring tool used for the Error Tracking Service.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>42, 74</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>['AU_17']</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>architecture based on microservices</t>
+          <t>Use Sentry to track and manage errors in the application</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CF_M09_AU17</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1889,12 +1933,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1907,7 +1951,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1917,29 +1961,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Error tracking tool.</t>
+          <t>Relational database engine used by the Data Service.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>42, 71</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_18']</t>
+          <t>['AU_07']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1949,7 +1993,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Use Sentry to track and manage errors in the application</t>
+          <t>Data Service (PostgreSQL)</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1957,13 +2001,13 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M09_AU17</t>
+          <t>CF_M09_AU07</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU08</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1971,12 +2015,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_AU07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1989,49 +2033,45 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Data Service</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Payment processing platform.</t>
+          <t>Service providing relational database storage.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>['AU_14']</t>
-        </is>
-      </c>
+          <t>41, 42</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Data Service</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Integrate with Stripe to handle payments and subscriptions</t>
+          <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -2039,13 +2079,13 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M09_AU13</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_AU07</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2053,12 +2093,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M08_AU08</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2071,7 +2111,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2081,29 +2121,29 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Relational database engine.</t>
+          <t>Framework used to build the System Service.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>42, 44</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_06']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2113,7 +2153,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL)</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2121,13 +2161,13 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
+          <t>CF_M00_AU04</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M08_AU08</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2135,17 +2175,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2153,55 +2193,59 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Component-Based</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The user interface is constructed using independent and reusable components that encapsulate their own logic, styles, and structure.</t>
+          <t>Core application service serving the web interface and business logic.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41, 42, 44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Component-based</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
+          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2209,12 +2253,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2227,7 +2271,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2237,29 +2281,29 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Analytics tool.</t>
+          <t>Reverse proxy and load balancer tool used for the Security Service.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41, 43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_16']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2269,21 +2313,21 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
+          <t>Security Service (Traefik)</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M09_AU15</t>
+          <t>CF_M00_AU02</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2291,35 +2335,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
+          <t>CF_M08_AU25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cloud storage provider.</t>
+          <t>The System Service (Next.js) interacts with the Authentication Service (Google).</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2329,29 +2369,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_04', 'AU_10']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>system service, authentication service</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Amazon S3 (for cloud)</t>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -2359,163 +2399,163 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M09_AU11</t>
+          <t>CF_M08_AU04, CF_M08_AU10</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>CF_M08_AU25</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>system service, authentication</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M08_AU01</t>
+          <t>CF_M08_AU26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Amazon EC2</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cloud infrastructure hosting the services.</t>
+          <t>The System Service (Next.js) interacts with the Storage Service (Amazon S3).</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_04', 'AU_06']</t>
+          <t>['AU_04', 'AU_11']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Amazon EC2</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>system service, storage service</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>These services run on Amazon EC2 instances</t>
+          <t>• Interacts with various external services for specific functionalities […] Cloud storage</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AU04, CF_M08_AU12</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M08_AU01</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>CF_M08_AU26</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>system service, cloud storage</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Next.js</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Web framework used for the System Service.</t>
+          <t>The System Service (Next.js) interacts with the Email Service (Brevo).</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>42, 44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_04', 'AU_19']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Next.js</t>
-        </is>
-      </c>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>system service, email service</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>System Service (Next.js)</t>
+          <t>• Interacts with various external services for specific functionalities [...] Correo electrónico</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2523,26 +2563,30 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M00_AU04</t>
+          <t>CF_M08_AU04, CF_M08_AU20</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>CF_M08_AU30</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>system service, email</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2555,45 +2599,49 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>System Service</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Core application service responsible for web rendering and business logic.</t>
+          <t>Cloud storage provider used for the Storage Service.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>41, 42</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>42, 73</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>['AU_11']</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>System Service</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
+          <t>Amazon S3 (for cloud)</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2601,13 +2649,13 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M09_AU11</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2615,12 +2663,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2633,59 +2681,63 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>React</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Reverse proxy and load balancer managing incoming HTTP/HTTPS traffic.</t>
+          <t>Library used for building user interfaces within the System Service.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>41, 43</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>42, 47</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>React</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>It serves the web application using React</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M00_AU04</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2693,12 +2745,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2711,53 +2763,49 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Containerization platform for managing service execution.</t>
+          <t>Reverse proxy and load balancer managing HTTP/HTTPS traffic.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41, 42, 76</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_04', 'AU_06']</t>
-        </is>
-      </c>
+          <t>41, 43</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Each of these services is contained in a Docker container</t>
+          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2767,7 +2815,7 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2775,12 +2823,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2793,45 +2841,49 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Service providing relational database storage.</t>
+          <t>Payment processing platform used for the Payment Service.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>42, 75</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>['AU_13']</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
+          <t>Integrate with Stripe to handle payments and subscriptions</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2839,16 +2891,250 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M09_AU13</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CF_M08_AU01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cloud infrastructure hosting the application services.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>These services run on Amazon EC2 instances</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>CF_M08_AU01</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CF_M08_AD03</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Component-Based</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>The user interface is constructed using independent and reusable components that encapsulate their own logic, styles, and structure.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Component-based</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>CF_M08_AD03</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CF_M08_AU17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Google Analytics</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Analytics tool used for the Analytics Service.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>['AU_15']</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Google Analytics</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CF_M09_AU15</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>CF_M08_AU17</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2861,7 +3147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2939,49 +3225,49 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0612</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Analytics Service</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reverse proxy and load balancer tool.</t>
+          <t>External service for tracking and analyzing site traffic.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Traffic</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.1492</v>
+        <v>0.7045</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2991,33 +3277,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>Error Tracking Service</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>External service for tracking and analyzing site traffic.</t>
+          <t>External service for monitoring and managing application errors.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7081</v>
+        <v>0.3288</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3033,7 +3319,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Email and marketing communication platform.</t>
+          <t>Email marketing and communication platform used for the Email Service.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3047,121 +3333,117 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.0576</v>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Server Component</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>user, security service</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Next.js component rendered on the server.</t>
+          <t>The User interacts with the Security Service (Traefik).</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Component-based</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.5143</v>
+        <v>0.5196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Client Component</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>security service, system service</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Next.js component rendered on the client.</t>
+          <t>The Security Service (Traefik) routes traffic to the System Service (Next.js).</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Component-based</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.4458</v>
+        <v>0.4728</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Server Action</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>system service, data service</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mechanism for client components to execute server-side logic.</t>
+          <t>The System Service (Next.js) communicates with the Data Service (PostgreSQL) using Prisma.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Observer</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.3876</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3172,32 +3454,32 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>user, security service</t>
+          <t>system service, payment service</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>User to Security Service connection.</t>
+          <t>The System Service (Next.js) interacts with the Payment Service (Stripe).</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.6226</v>
+        <v>0.4509</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3208,32 +3490,32 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>security service, system service</t>
+          <t>system service, analytics service</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Security Service to System Service connection.</t>
+          <t>The System Service (Next.js) interacts with the Analytics Service (Google Analytics).</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.6706</v>
+        <v>0.6371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3244,68 +3526,68 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>system service, data service</t>
+          <t>system service, error tracking service</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>System Service to Data Service connection.</t>
+          <t>The System Service (Next.js) interacts with the Error Tracking Service (Sentry).</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.6829</v>
+        <v>0.4196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Reverse Proxy</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>user, system service</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
+          <t>The User interacts with the System Service (Next.js) via client components.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.0669</v>
+        <v>0.3259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3315,33 +3597,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Load Balancer</t>
+          <t>Reverse Proxy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Traefik distributes incoming traffic across multiple service instances to improve availability and responsiveness.</t>
+          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.021</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P_07</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3351,27 +3633,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ORM (Object-Relational Mapping)</t>
+          <t>Load Balancer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Traefik distributes incoming traffic across multiple service instances to improve availability and responsiveness.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CF_M08_AU22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0226</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P_07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ORM (Object-Relational Mapping)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>CF_M08_AD02</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>ORM</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>0.3274</v>
+      <c r="H15" t="n">
+        <v>0.3491</v>
       </c>
     </row>
   </sheetData>
@@ -3385,7 +3703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3433,43 +3751,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Traffic</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>system service, postgresql</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Traefik</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1492</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
+          <t>CF_M08_AU27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3480,68 +3794,64 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>system service, postgresql</t>
+          <t>system service, payment processing</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Payment Service</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.4805</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>system service, analysis</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>It serves the web application using React</t>
+          <t>• Interacts with various external services for specific functionalities […] Analysis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Reverse Proxy</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.0467</v>
+        <v>0.2504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3552,382 +3862,274 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>system service, authentication</t>
+          <t>system service, error monitoring</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Authentication Service</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.501</v>
+        <v>0.2517</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_AU26</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>system service, cloud storage</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Cloud storage</t>
+          <t>Use Google for user authentication</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Storage Service</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.371</v>
+        <v>0.6296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_AU27</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>system service, payment processing</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Payment Service</t>
+          <t>Analytics Service</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3477</v>
+        <v>0.2918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AU28</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>system service, analysis</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Error monitoring</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Analysis</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>Error Tracking Service</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.1953</v>
+        <v>0.3288</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AU29</t>
+          <t>CF_M08_AU21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>system service, error monitoring</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Briefly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
+          <t>Connects to Brevo to create, send and schedule emails.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Monitoring Service</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.4194</v>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AU30</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>system service, email</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Correo electrónico</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>0.1083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_AU16</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>ORM (Object-Relational Mapping)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.2935</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M08_AU21</t>
+          <t>CF_M08_AD06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Briefly</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Connects to Brevo to create, send and schedule emails.</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Brevo</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.0576</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M08_AU23</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>HTTPS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M08_AD02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Prisma ORM</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CF_M08_AD06</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Client Component</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0.3476</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.8205</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6667</v>
+        <v>0.8889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7241</v>
+        <v>0.8667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7241</v>
+        <v>0.8966</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8478</v>
+        <v>0.8609</v>
       </c>
     </row>
     <row r="6">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24</v>
+        <v>0.2188</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2576</v>
+        <v>0.2344</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.96</v>
+        <v>0.9688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1875</v>
+        <v>0.24</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>23</v>
       </c>
       <c r="C2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2" t="n">
         <v>22</v>
       </c>
-      <c r="D2" t="n">
-        <v>18</v>
-      </c>
       <c r="E2" t="n">
-        <v>0.8182</v>
+        <v>0.9565</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7826</v>
+        <v>0.9565</v>
       </c>
     </row>
     <row r="3">
@@ -670,16 +670,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.6667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4286</v>
+        <v>0.8571</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.8205</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6667</v>
+        <v>0.8889</v>
       </c>
     </row>
     <row r="10">
@@ -864,22 +864,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -895,19 +895,19 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -923,19 +923,19 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -951,19 +951,19 @@
         <v>39</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -976,22 +976,22 @@
         <v>30</v>
       </c>
       <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="n">
         <v>28</v>
       </c>
-      <c r="D6" t="n">
-        <v>21</v>
-      </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,12 +1141,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1155,26 +1155,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5289</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Payment Service</t>
+          <t>Prisma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>External service for handling payments and subscriptions.</t>
+          <t>ORM tool used to manage database queries and schema.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>42, 50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1185,23 +1185,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>Prism</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>Prisma as ORM</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -1209,13 +1209,13 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1223,12 +1223,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1237,11 +1237,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6022</v>
+        <v>0.6908</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Prisma</t>
+          <t>Google OAuth</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1251,29 +1251,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ORM tool used to manage database access.</t>
+          <t>Third-party provider for user authentication.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42, 50</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_10']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Prism</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Prisma as ORM</t>
+          <t>Use Google for user authentication</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1291,13 +1291,13 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M09_AU09</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1305,81 +1305,73 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M08_AU12</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6508</v>
+        <v>0.716</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Storage Service</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>External cloud storage service for files.</t>
+          <t>Used to establish a one-to-many relationship where objects (observers) subscribe to a subject to receive notifications of state changes, implemented via event listeners.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['AU_04']</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Cloud storage</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Cloud storage</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M08_AU12</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1387,12 +1379,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1401,11 +1393,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7157</v>
+        <v>0.757</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>Singleton Pattern</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1415,25 +1407,25 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Establishes a one-to-many relationship where subjects notify observers of state changes, implemented via event listeners in components.</t>
+          <t>Ensures a class has only one instance and provides a global access point to it, used here to manage the PrismaClient instance.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Singleton</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1443,17 +1435,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1461,73 +1453,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7595</v>
+        <v>0.8565</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Singleton Pattern</t>
+          <t>Email Service</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ensures a class has only one instance and provides a global access point, used here to manage the PrismaClient instance.</t>
+          <t>External service for sending and scheduling emails.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Singleton</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1535,12 +1535,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8984</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Email Service</t>
+          <t>Analytics Service</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>External service for sending and managing emails.</t>
+          <t>External service for tracking and analyzing site traffic.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1579,13 +1579,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1603,13 +1603,13 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1617,12 +1617,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_AU12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9391</v>
+        <v>0.926</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>Cloud Storage Service</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>External service for user authentication via Google.</t>
+          <t>External service for storing and retrieving files.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1661,13 +1661,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Cloud storage</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Cloud storage</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1685,13 +1685,13 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_AU12</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1699,73 +1699,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.9367</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The system is built as a collection of small, independent services (Security Service, System Service, Data Service) that communicate with each other and are managed as Docker containers.</t>
+          <t>External service for user authentication.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>architecture based on microservices</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1773,12 +1781,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1787,49 +1795,53 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.9401</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Error Monitoring Service</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Containerization platform used to manage and run services.</t>
+          <t>External service for tracking and managing application errors.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>41, 76</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Each of these services is contained in a Docker container</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1837,13 +1849,13 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1851,12 +1863,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1865,53 +1877,53 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.9458</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Payment Processing Service</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Error monitoring tool used for the Error Tracking Service.</t>
+          <t>External service for handling payments and subscriptions.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>42, 74</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['AU_17']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Use Sentry to track and manage errors in the application</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1919,13 +1931,13 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M09_AU17</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1961,7 +1973,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Relational database engine used by the Data Service.</t>
+          <t>Relational database engine used for the Data Service.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2015,12 +2027,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2033,45 +2045,49 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>React</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Service providing relational database storage.</t>
+          <t>Library for building user interfaces within the System Service.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>41, 42</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>42, 47</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>React</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
+          <t>It serves the web application using React</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -2079,13 +2095,13 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M00_AU04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2121,7 +2137,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Framework used to build the System Service.</t>
+          <t>Web framework used to build the System Service.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2175,63 +2191,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Core application service serving the web interface and business logic.</t>
+          <t>The System Service interacts with the Authentication Service (Google OAuth).</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41, 42, 44</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>['AU_04', 'AU_10']</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>system service, authentication service</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -2239,108 +2255,112 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AU04, CF_M08_AU10</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>CF_M08_AU25</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>system service, authentication</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Traefik</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Reverse proxy and load balancer tool used for the Security Service.</t>
+          <t>The System Service interacts with the Cloud Storage Service (Amazon S3).</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>41, 43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_04', 'AU_12']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Traefik</t>
-        </is>
-      </c>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>system service, cloud storage service</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>• Interacts with various external services for specific functionalities […] Cloud storage</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M00_AU02</t>
+          <t>CF_M08_AU04, CF_M08_AU12</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>CF_M08_AU26</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>system service, cloud storage</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2359,7 +2379,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The System Service (Next.js) interacts with the Authentication Service (Google).</t>
+          <t>The System Service interacts with the Payment Processing Service (Stripe).</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2369,18 +2389,18 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_10']</t>
+          <t>['AU_04', 'AU_14']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>system service, authentication service</t>
+          <t>system service, payment processing service</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2391,7 +2411,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -2399,30 +2419,30 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU10</t>
+          <t>CF_M08_AU04, CF_M08_AU14</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU27</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>system service, authentication</t>
+          <t>system service, payment processing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M08_AU26</t>
+          <t>CF_M08_AU28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2441,7 +2461,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The System Service (Next.js) interacts with the Storage Service (Amazon S3).</t>
+          <t>The System Service interacts with the Analytics Service (Google Analytics).</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2451,18 +2471,18 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_11']</t>
+          <t>['AU_04', 'AU_16']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>system service, storage service</t>
+          <t>system service, analytics service</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2473,7 +2493,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Cloud storage</t>
+          <t>• Interacts with various external services for specific functionalities […] Analysis</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2481,18 +2501,18 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU12</t>
+          <t>CF_M08_AU04, CF_M08_AU16</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M08_AU26</t>
+          <t>CF_M08_AU28</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>system service, cloud storage</t>
+          <t>system service, analytics</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2524,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M08_AU30</t>
+          <t>CF_M08_AU29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2523,7 +2543,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The System Service (Next.js) interacts with the Email Service (Brevo).</t>
+          <t>The System Service interacts with the Error Monitoring Service (Sentry).</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2533,7 +2553,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_19']</t>
+          <t>['AU_04', 'AU_18']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2544,7 +2564,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>system service, email service</t>
+          <t>system service, error monitoring service</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2555,7 +2575,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Correo electrónico</t>
+          <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2563,85 +2583,81 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU20</t>
+          <t>CF_M08_AU04, CF_M08_AU18</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M08_AU30</t>
+          <t>CF_M08_AU29</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>system service, email</t>
+          <t>system service, error monitoring</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
+          <t>CF_M08_AU30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cloud storage provider used for the Storage Service.</t>
+          <t>The System Service interacts with the Email Service (Brevo).</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>42, 73</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_11']</t>
+          <t>['AU_04', 'AU_20']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>system service, email service</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Amazon S3 (for cloud)</t>
+          <t>• Interacts with various external services for specific functionalities [...] Correo electrónico</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2649,31 +2665,35 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M09_AU11</t>
+          <t>CF_M08_AU04, CF_M08_AU20</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>CF_M08_AU30</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>system service, email</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_P03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2681,63 +2701,55 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Component-Based</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Library used for building user interfaces within the System Service.</t>
+          <t>The user interface is constructed using independent and reusable components that encapsulate their own logic, styles, and structure.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>42, 47</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['AU_04']</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Component-based</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>It serves the web application using React</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>CF_M00_AU04</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_P03</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2745,12 +2757,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2763,59 +2775,63 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Reverse proxy and load balancer managing HTTP/HTTPS traffic.</t>
+          <t>Containerization platform used to manage and run the system services.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41, 43</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>41, 76</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>['AU_02', 'AU_04', 'AU_07']</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>Each of these services is contained in a Docker container</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2823,12 +2839,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_AU21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2841,7 +2857,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2851,29 +2867,29 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Payment processing platform used for the Payment Service.</t>
+          <t>Third-party email and marketing communication platform.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>42, 75</t>
+          <t>42, 73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_20']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2883,7 +2899,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Integrate with Stripe to handle payments and subscriptions</t>
+          <t>Connects to Brevo to create, send and schedule emails.</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2891,13 +2907,13 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M09_AU13</t>
+          <t>CF_M09_AU19</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_AU21</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2905,12 +2921,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M08_AU01</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2923,7 +2939,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Amazon EC2</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2933,25 +2949,29 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cloud infrastructure hosting the application services.</t>
+          <t>Third-party error tracking tool.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>42, 74</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>['AU_18']</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Amazon EC2</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2961,21 +2981,21 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>These services run on Amazon EC2 instances</t>
+          <t>Use Sentry to track and manage errors in the application</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M09_AU17</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M08_AU01</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2983,17 +3003,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3001,55 +3021,63 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Component-Based</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The user interface is constructed using independent and reusable components that encapsulate their own logic, styles, and structure.</t>
+          <t>Third-party analytics tool.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>['AU_16']</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Component-based</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CF_M09_AU15</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3057,12 +3085,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3075,7 +3103,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3085,29 +3113,29 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Analytics tool used for the Analytics Service.</t>
+          <t>Cloud storage provider used for file management.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>42, 73</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3117,7 +3145,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
+          <t>Amazon S3 (for cloud)</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -3125,16 +3153,570 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M09_AU15</t>
+          <t>CF_M09_AU11</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CF_M08_AU07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Service</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Service providing relational database storage.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>42, 68</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Data Service</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CF_M08_AU07</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Traefik</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Reverse proxy and load balancer tool used to implement the Security Service.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>41, 43</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>['AU_02']</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Traefik</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Security Service (Traefik)</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CF_M00_AU02</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CF_M08_AU02</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Security Service</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Reverse proxy and load balancer managing HTTP/HTTPS traffic.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>41, 43</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Security Service</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>CF_M08_AU02</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CF_M08_AU15</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Third-party payment processing platform.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>42, 75</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>['AU_14']</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Integrate with Stripe to handle payments and subscriptions</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CF_M09_AU13</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>CF_M08_AU15</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>The system is built as a collection of small, independent services (Security Service, System Service, Data Service) that communicate with each other and are managed as Docker containers.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>architecture based on microservices</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CF_M08_AU01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cloud infrastructure hosting the system containers.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>['AU_02', 'AU_04', 'AU_07']</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>These services run on Amazon EC2 instances</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>CF_M08_AU01</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CF_M08_AU04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>System Service</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Core application service handling web rendering and business logic.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>42, 44</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>System Service</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>CF_M08_AU04</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3147,7 +3729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3211,12 +3793,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Individual or entity (donor or company) that interacts with the system.</t>
+          <t>Any individual or entity that interacts with the system, including donors and companies.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3225,470 +3807,218 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0643</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analytics Service</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>user, security service</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>External service for tracking and analyzing site traffic.</t>
+          <t>The User interacts with the Security Service (Traefik) to access the system.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7045</v>
+        <v>0.4305</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Error Tracking Service</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>security service, system service</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>External service for monitoring and managing application errors.</t>
+          <t>The Security Service (Traefik) routes HTTP/HTTPS traffic to the System Service.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3288</v>
+        <v>0.4206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Brevo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>system service, data service</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Email marketing and communication platform used for the Email Service.</t>
+          <t>The System Service communicates with the Data Service (PostgreSQL) using Prisma.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M08_AU21</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Briefly</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.0602</v>
+        <v>0.6284999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>user, security service</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Reverse Proxy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The User interacts with the Security Service (Traefik).</t>
+          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.5196</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>security service, system service</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Load Balancer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Security Service (Traefik) routes traffic to the System Service (Next.js).</t>
+          <t>Traefik distributes incoming traffic across multiple instances of services to improve availability and responsiveness.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.4728</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>P_07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>system service, data service</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ORM (Object-Relational Mapping)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The System Service (Next.js) communicates with the Data Service (PostgreSQL) using Prisma.</t>
+          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M08_P02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ORM</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>0.5987</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>system service, payment service</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>The System Service (Next.js) interacts with the Payment Service (Stripe).</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4509</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>system service, analytics service</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>The System Service (Next.js) interacts with the Analytics Service (Google Analytics).</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M08_AU17</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Google Analytics</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.6371</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>system service, error tracking service</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>The System Service (Next.js) interacts with the Error Tracking Service (Sentry).</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4196</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>user, system service</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>The User interacts with the System Service (Next.js) via client components.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.3259</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Reverse Proxy</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CF_M08_AU14</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Payment processing</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0675</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Load Balancer</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Traefik distributes incoming traffic across multiple service instances to improve availability and responsiveness.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CF_M08_AU22</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0226</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ORM (Object-Relational Mapping)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CF_M08_AD02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
         <v>0.3491</v>
       </c>
     </row>
@@ -3703,7 +4033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3772,364 +4102,116 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.5987</v>
+        <v>0.6284999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AU27</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>system service, payment processing</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Payment Service</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.3422</v>
+        <v>0.3524</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AU28</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>system service, analysis</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ORM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Analysis</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>P_07</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ORM (Object-Relational Mapping)</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.2504</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AU29</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>system service, error monitoring</t>
-        </is>
-      </c>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Observer Pattern</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0.2517</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CF_M08_AU11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Use Google for user authentication</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Google Analytics</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6296</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M08_AU16</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analysis</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Analysis</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Analytics Service</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.2918</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CF_M08_AU18</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Error monitoring</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Error monitoring</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Error Tracking Service</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3288</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M08_AU21</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Briefly</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Connects to Brevo to create, send and schedule emails.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Brevo</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0602</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M08_AU23</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HTTPS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M08_AD02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ORM (Object-Relational Mapping)</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.3491</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M08_AD06</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Observer Pattern</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.24</v>
+        <v>0.2343</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
@@ -447,14 +447,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>all elements (name | isPartOf)</t>
+          <t>all elements (units/patterns by name, connectors by unit-pair)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8205</v>
+        <v>0.8462</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8889</v>
+        <v>0.9167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8667</v>
+        <v>0.931</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8966</v>
+        <v>0.931</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8609</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="6">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2188</v>
+        <v>0.6429</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2344</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9688</v>
+        <v>0.8571</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24</v>
+        <v>0.4348</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9565</v>
+        <v>0.9167</v>
       </c>
       <c r="F2" t="n">
         <v>0.9565</v>
@@ -648,35 +648,35 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5714</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6667</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>connector (unit-pairs)</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6667</v>
+        <v>0.6</v>
       </c>
       <c r="F4" t="n">
         <v>0.8571</v>
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -725,77 +725,101 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>True Positives (matched)</t>
+          <t>True Positives (matched elements)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Validated correct (name for units/patterns, isPartOf for connectors)</t>
+          <t>Named correct (units/patterns by name)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>False Positives</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>7</v>
+          <t>Connector unit-pairs (GT / LLM)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7 / 10</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>False Negatives</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
+          <t>Connector pair TP (recall / precision)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6 / 6</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Precision (all elements; units/patterns by name, connectors by isPartOf)</t>
+          <t>False Positives</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8205</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Recall (all elements; units/patterns by name, connectors by isPartOf)</t>
+          <t>False Negatives</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8889</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Precision (units/patterns by name, connectors by unit-pair)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8462</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Recall (units/patterns by name, connectors by unit-pair)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9167</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Match threshold (cosine)</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0.35</v>
+      <c r="B12" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -864,22 +888,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -889,25 +913,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -917,25 +941,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -945,25 +969,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -973,25 +997,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
         <v>28</v>
-      </c>
-      <c r="E6" t="n">
-        <v>25</v>
-      </c>
-      <c r="F6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,81 +1165,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Prisma</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ORM tool used to manage database queries and schema.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42, 50</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['AU_04']</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Prism</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Prisma as ORM</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>CF_M08_P02</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1223,81 +1239,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6908</v>
+        <v>0.891</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Google OAuth</t>
+          <t>Singleton Pattern</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Third-party provider for user authentication.</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>['AU_10']</t>
-        </is>
-      </c>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Singleton</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Use Google for user authentication</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CF_M09_AU09</t>
-        </is>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1305,73 +1313,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M08_P04</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.716</v>
+        <v>0.8952</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Used to establish a one-to-many relationship where objects (observers) subscribe to a subject to receive notifications of state changes, implemented via event listeners.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M08_P04</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1379,73 +1395,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M08_P05</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.757</v>
+        <v>0.9058</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Singleton Pattern</t>
+          <t>Email Service</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ensures a class has only one instance and provides a global access point to it, used here to manage the PrismaClient instance.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Singleton</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M08_P05</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1453,12 +1477,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1467,11 +1491,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8565</v>
+        <v>0.9096</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Email Service</t>
+          <t>Analytics Service</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1481,7 +1505,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>External service for sending and scheduling emails.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1491,19 +1515,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1513,7 +1537,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1527,7 +1551,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1540,7 +1564,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M08_AU16</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1549,11 +1573,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8984</v>
+        <v>0.91</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>Error Monitoring Service</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1563,7 +1587,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>External service for tracking and analyzing site traffic.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1573,7 +1597,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1585,7 +1609,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1595,7 +1619,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1609,7 +1633,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M08_AU16</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1617,12 +1641,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M08_AU12</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1631,21 +1655,21 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.926</v>
+        <v>0.9159</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cloud Storage Service</t>
+          <t>Prisma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>External service for storing and retrieving files.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1655,29 +1679,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['P_05']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Cloud storage</t>
+          <t>Prism</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Cloud storage</t>
+          <t>Prisma as ORM</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1685,13 +1709,13 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M08_AU12</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1699,12 +1723,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1713,11 +1737,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9367</v>
+        <v>0.9391</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>Payment Processing Service</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1727,7 +1751,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>External service for user authentication.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1737,19 +1761,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1759,7 +1783,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1773,7 +1797,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1781,12 +1805,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_AU12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1795,11 +1819,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9401</v>
+        <v>0.9431</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Error Monitoring Service</t>
+          <t>Cloud Storage Service</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1809,7 +1833,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>External service for tracking and managing application errors.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1819,19 +1843,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Cloud storage</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1841,7 +1865,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Cloud storage</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1855,7 +1879,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_AU12</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1863,81 +1887,73 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_P03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9458</v>
+        <v>0.9946</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Payment Processing Service</t>
+          <t>Component-Based</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>External service for handling payments and subscriptions.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['AU_04']</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>Component-based</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_P03</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1945,12 +1961,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M08_AU08</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,63 +1979,63 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Relational database engine used for the Data Service.</t>
+          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: Security Service (Traefik).</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42, 71</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_07']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL)</t>
+          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M08_AU08</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2027,12 +2043,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2045,7 +2061,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Amazon EC2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2055,29 +2071,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Library for building user interfaces within the System Service.</t>
+          <t>Dichos servicios se ejecutan en instancias de Amazon EC2.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>42, 47</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Amazon EC2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2087,21 +2103,21 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>It serves the web application using React</t>
+          <t>These services run on Amazon EC2 instances</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M00_AU04</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU01</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2109,12 +2125,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2127,7 +2143,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2137,29 +2153,29 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Web framework used to build the System Service.</t>
+          <t>Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>42, 44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_18']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2169,7 +2185,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>System Service (Next.js)</t>
+          <t>Connects to Brevo to create, send and schedule emails.</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2177,13 +2193,13 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M00_AU04</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU21</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2191,63 +2207,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Service</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The System Service interacts with the Authentication Service (Google OAuth).</t>
+          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: Data Service (PostgreSQL).</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41, 42</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_10']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>system service, authentication service</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Data Service</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -2255,49 +2275,49 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU10</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>system service, authentication</t>
-        </is>
-      </c>
+          <t>CF_M08_AU07</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M08_AU26</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sentry</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The System Service interacts with the Cloud Storage Service (Amazon S3).</t>
+          <t>Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2307,29 +2327,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_12']</t>
+          <t>['AU_16']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>system service, cloud storage service</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Sentry</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Cloud storage</t>
+          <t>Use Sentry to track and manage errors in the application</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2337,81 +2357,81 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU12</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M08_AU26</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>system service, cloud storage</t>
-        </is>
-      </c>
+          <t>CF_M08_AU19</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M08_AU27</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The System Service interacts with the Payment Processing Service (Stripe).</t>
+          <t>Dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_14']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>system service, payment processing service</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Payment processing</t>
+          <t>Each of these services is contained in a Docker container</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -2419,30 +2439,26 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU14</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M08_AU27</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>system service, payment processing</t>
-        </is>
-      </c>
+          <t>CF_M08_AU22</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M08_AU28</t>
+          <t>CF_M08_AU25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2461,7 +2477,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The System Service interacts with the Analytics Service (Google Analytics).</t>
+          <t>System Service (Next.js) interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2471,18 +2487,18 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_16']</t>
+          <t>['AU_03', 'AU_08', 'AU_10', 'AU_12', 'AU_14', 'AU_16', 'AU_18']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>system service, analytics service</t>
+          <t>system service, authentication service, cloud storage service, payment processing service, analytics service, error monitoring service, email service</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2493,7 +2509,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities […] Analysis</t>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2501,49 +2517,53 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU16</t>
+          <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M08_AU28</t>
+          <t>CF_M08_AU25</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>system service, analytics</t>
+          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M08_AU29</t>
+          <t>CF_M08_AU08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The System Service interacts with the Error Monitoring Service (Sentry).</t>
+          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2553,29 +2573,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_18']</t>
+          <t>['AU_05']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>system service, error monitoring service</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>AU_06</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Error monitoring</t>
+          <t>Data Service (PostgreSQL)</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2583,49 +2603,49 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU18</t>
+          <t>CF_M08_AU07</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M08_AU29</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>system service, error monitoring</t>
-        </is>
-      </c>
+          <t>CF_M08_AU08</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M08_AU30</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The System Service interacts with the Email Service (Brevo).</t>
+          <t>Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2635,29 +2655,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_20']</t>
+          <t>['AU_08']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>system service, email service</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Correo electrónico</t>
+          <t>Use Google for user authentication</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2665,35 +2685,31 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU20</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M08_AU30</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>system service, email</t>
-        </is>
-      </c>
+          <t>CF_M08_AU11</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M08_P03</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2701,55 +2717,63 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Component-Based</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>The user interface is constructed using independent and reusable components that encapsulate their own logic, styles, and structure.</t>
+          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['AU_10']</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Component-based</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
+          <t>Amazon S3 (for cloud)</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CF_M08_AU11</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M08_P03</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2757,17 +2781,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2775,49 +2799,45 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Containerization platform used to manage and run the system services.</t>
+          <t>It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41, 76</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_04', 'AU_07']</t>
-        </is>
-      </c>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Each of these services is contained in a Docker container</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2825,13 +2845,13 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2839,12 +2859,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M08_AU21</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2857,7 +2877,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brevo</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2867,29 +2887,29 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Third-party email and marketing communication platform.</t>
+          <t>Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>42, 73</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['AU_20']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Brevo</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2899,7 +2919,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Connects to Brevo to create, send and schedule emails.</t>
+          <t>Integrate with Stripe to handle payments and subscriptions</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2907,13 +2927,13 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M09_AU19</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M08_AU21</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2921,12 +2941,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2939,7 +2959,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2949,29 +2969,29 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Third-party error tracking tool.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>42, 74</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_18']</t>
+          <t>['AU_01']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2981,21 +3001,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Use Sentry to track and manage errors in the application</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>CF_M09_AU17</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3003,17 +3019,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3021,63 +3037,55 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Third-party analytics tool.</t>
+          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['AU_16']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
+          <t>architecture based on microservices</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>CF_M09_AU15</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3085,12 +3093,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3103,7 +3111,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3113,29 +3121,29 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cloud storage provider used for file management.</t>
+          <t>Traefik es un proxy inverso y balanceador de carga moderno diseñado para gestionar la entrada y salida de tráfico HTTP y HTTPS en aplicaciones basadas en contenedores.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>42, 73</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_01']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3145,21 +3153,21 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Amazon S3 (for cloud)</t>
+          <t>Security Service (Traefik)</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M09_AU11</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3167,12 +3175,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3185,7 +3193,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3195,25 +3203,29 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Service providing relational database storage.</t>
+          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: System Service (Next.js).</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>42, 68</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>41, 42</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>['P_01']</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3223,7 +3235,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
+          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -3237,7 +3249,7 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3245,12 +3257,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3263,7 +3275,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3273,29 +3285,29 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Reverse proxy and load balancer tool used to implement the Security Service.</t>
+          <t>Next.js es un framework para la creación de aplicaciones web que ofrece una estructura adicional, características y optimizaciones que permiten construir aplicaciones más rápido.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>41, 43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3305,21 +3317,21 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CF_M00_AU02</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3327,12 +3339,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3345,378 +3357,66 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Reverse proxy and load balancer managing HTTP/HTTPS traffic.</t>
+          <t>Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>41, 43</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>['AU_14']</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CF_M08_AU15</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Third-party payment processing platform.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>42, 75</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>['AU_14']</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Integrate with Stripe to handle payments and subscriptions</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>CF_M09_AU13</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>CF_M08_AU15</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>The system is built as a collection of small, independent services (Security Service, System Service, Data Service) that communicate with each other and are managed as Docker containers.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>architecture based on microservices</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>CF_M08_AU01</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Amazon EC2</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Cloud infrastructure hosting the system containers.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_04', 'AU_07']</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Amazon EC2</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>These services run on Amazon EC2 instances</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>CF_M08_AU01</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Core application service handling web rendering and business logic.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>42, 44</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>System Service</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3729,7 +3429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3777,37 +3477,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Any individual or entity that interacts with the system, including donors and companies.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_P04</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0639</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="3">
@@ -3818,32 +3518,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>user, security service</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The User interacts with the Security Service (Traefik) to access the system.</t>
+          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.4305</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="4">
@@ -3860,26 +3560,26 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>security service, system service</t>
+          <t>traefik, system service</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The Security Service (Traefik) routes HTTP/HTTPS traffic to the System Service.</t>
+          <t>Traefik gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.4206</v>
+        <v>0.7524</v>
       </c>
     </row>
     <row r="5">
@@ -3901,7 +3601,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The System Service communicates with the Data Service (PostgreSQL) using Prisma.</t>
+          <t>System Service (Next.js) se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3911,115 +3611,75 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.8296</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Reverse Proxy</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>data service, prisma</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Traefik acts as an intermediary for client requests, redirecting incoming traffic to the appropriate internal services.</t>
+          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Payment processing</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.0598</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Load Balancer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>user, system service</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Traefik distributes incoming traffic across multiple instances of services to improve availability and responsiveness.</t>
+          <t>Un usuario es todo individuo o entidad que interactúa con el sistema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.0242</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ORM (Object-Relational Mapping)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Technique used to convert data between the object-oriented programming system and the relational database, implemented via Prisma.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CF_M08_P02</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3491</v>
+        <v>0.6612</v>
       </c>
     </row>
   </sheetData>
@@ -4033,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4102,18 +3762,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4123,95 +3783,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>React</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
+          <t>It serves the web application using React</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>0.3524</v>
+        <v>0.6719000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>P_07</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ORM (Object-Relational Mapping)</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3491</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CF_M08_P06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Observer Pattern</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2343</v>
+        <v>0.727</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.931</v>
+        <v>0.9</v>
       </c>
       <c r="C3" t="n">
         <v>0.931</v>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6429</v>
+        <v>0.75</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8262</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8571</v>
+        <v>0.75</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4348</v>
+        <v>0.2963</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
         <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9167</v>
+        <v>0.88</v>
       </c>
       <c r="F2" t="n">
         <v>0.9565</v>
@@ -670,13 +670,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F4" t="n">
         <v>0.8571</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 10</t>
+          <t>7 / 9</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -888,7 +888,7 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
         <v>27</v>
@@ -916,7 +916,7 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
         <v>28</v>
@@ -944,7 +944,7 @@
         <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
         <v>28</v>
@@ -956,7 +956,7 @@
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
         <v>28</v>
@@ -972,7 +972,7 @@
         <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
         <v>28</v>
@@ -984,7 +984,7 @@
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
         <v>28</v>
@@ -1000,19 +1000,19 @@
         <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
         <v>23</v>
       </c>
       <c r="E6" t="n">
+        <v>27</v>
+      </c>
+      <c r="F6" t="n">
         <v>23</v>
       </c>
-      <c r="F6" t="n">
-        <v>22</v>
-      </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
         <v>28</v>
@@ -1201,7 +1201,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>['P_01', 'AU_04']</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
@@ -1275,7 +1279,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>['P_01', 'AU_04']</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
@@ -1351,7 +1359,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1433,7 +1441,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1515,7 +1523,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1597,7 +1605,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1641,7 +1649,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1679,13 +1687,13 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['P_05']</t>
+          <t>['AU_04', 'P_05']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1761,7 +1769,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1843,7 +1851,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1923,7 +1931,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>['P_01', 'AU_04']</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -1961,7 +1973,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2005,7 +2017,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2043,12 +2055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M08_AU01</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2061,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazon EC2</t>
+          <t>React</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2071,29 +2083,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dichos servicios se ejecutan en instancias de Amazon EC2.</t>
+          <t>React es una biblioteca de JavaScript de código abierto diseñada para construir interfaces de usuario (UI) de manera eficiente y flexible.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Amazon EC2</t>
+          <t>React</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2103,21 +2115,21 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>These services run on Amazon EC2 instances</t>
+          <t>It serves the web application using React</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M08_AU01</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2207,7 +2219,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2240,7 +2252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41, 42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2251,7 +2263,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2409,7 +2421,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_02', 'AU_04', 'AU_06']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2453,7 +2465,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2477,7 +2489,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>System Service (Next.js) interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2487,13 +2499,13 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_03', 'AU_08', 'AU_10', 'AU_12', 'AU_14', 'AU_16', 'AU_18']</t>
+          <t>['AU_04', 'AU_08', 'AU_10', 'AU_12', 'AU_14', 'AU_16', 'AU_18']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2535,7 +2547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2563,7 +2575,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
+          <t>Data Service (PostgreSQL) proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2573,13 +2585,13 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_05']</t>
+          <t>['AU_06']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2817,7 +2829,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>['P_01', 'AU_04']</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
@@ -2979,7 +2995,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3093,7 +3109,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3121,7 +3137,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Traefik es un proxy inverso y balanceador de carga moderno diseñado para gestionar la entrada y salida de tráfico HTTP y HTTPS en aplicaciones basadas en contenedores.</t>
+          <t>Como se puede observar en la figura 6, el Security Service está compuesto exclusivamente por ciertas funcionalidades de la herramienta Traefik.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3131,13 +3147,13 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3175,7 +3191,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3208,7 +3224,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>41, 42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3219,7 +3235,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3257,7 +3273,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3285,7 +3301,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Next.js es un framework para la creación de aplicaciones web que ofrece una estructura adicional, características y optimizaciones que permiten construir aplicaciones más rápido.</t>
+          <t>Como se puede observar en la figura 6, el System Service está principalmente desarrollado en Next.js.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3295,13 +3311,13 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3429,7 +3445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3477,109 +3493,109 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>User</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.894</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_P06</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.714</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>traefik, system service</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Traefik gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7524</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3596,28 +3612,32 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>system service, data service</t>
+          <t>security service, system service</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>System Service (Next.js) se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0.8296</v>
+        <v>0.7444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3628,12 +3648,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>data service, prisma</t>
+          <t>system service, data service</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3643,7 +3663,7 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.8529</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="7">
@@ -3660,26 +3680,58 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>user, system service</t>
+          <t>data service, prisma</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Un usuario es todo individuo o entidad que interactúa con el sistema</t>
+          <t>Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.7562</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>system service, system service</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Al interactuar con un componente de cliente, este puede acceder al servidor mediante el uso de las server actions.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>CF_M08_P06</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>0.6612</v>
+      <c r="H8" t="n">
+        <v>0.8107</v>
       </c>
     </row>
   </sheetData>
@@ -3741,69 +3793,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
+          <t>CF_M08_AU01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>system service, postgresql</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>• It communicates with the PostgreSQL database service</t>
+          <t>These services run on Amazon EC2 instances</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>0.8529</v>
+        <v>0.7938</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>system service, postgresql</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>It serves the web application using React</t>
+          <t>• It communicates with the PostgreSQL database service</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="4">
@@ -3830,16 +3882,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.727</v>
+        <v>0.8107</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8462</v>
+        <v>0.6842</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9167</v>
+        <v>0.7222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9</v>
+        <v>0.9286</v>
       </c>
       <c r="C3" t="n">
-        <v>0.931</v>
+        <v>0.8966</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9678</v>
+        <v>0.9552</v>
       </c>
     </row>
     <row r="6">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.75</v>
+        <v>0.8462</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8262</v>
+        <v>0.8267</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.75</v>
+        <v>0.9615</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2963</v>
+        <v>0.12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>0.88</v>
+        <v>0.913</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9565</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="3">
@@ -670,16 +670,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6667</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 9</t>
+          <t>7 / 10</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6 / 6</t>
+          <t>0 / 0</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8462</v>
+        <v>0.6842</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9167</v>
+        <v>0.7222</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +888,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +916,22 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +944,22 @@
         <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -972,22 +972,22 @@
         <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -1000,22 +1000,22 @@
         <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,77 +1165,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_P04</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.825</v>
+        <v>0.7743</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>Monitoring Service</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_04']</t>
+          <t>['AU_04', 'P_01']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M08_P04</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1243,77 +1247,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_P05</t>
+          <t>CF_M08_AU12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.891</v>
+        <v>0.8204</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Singleton Pattern</t>
+          <t>Storage Service</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_04']</t>
+          <t>['AU_04', 'P_01']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Singleton</t>
+          <t>Cloud storage</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
+          <t>Cloud storage</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M08_P05</t>
+          <t>CF_M08_AU12</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1321,81 +1329,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8952</v>
+        <v>0.825</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['P_01', 'AU_04']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1403,81 +1407,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9058</v>
+        <v>0.891</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Email Service</t>
+          <t>Singleton Pattern</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['P_01', 'AU_06']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Singleton</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1485,12 +1485,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M08_AU16</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1499,11 +1499,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9096</v>
+        <v>0.8952</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1523,19 +1523,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_04', 'P_01']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1559,7 +1559,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M08_AU16</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1567,12 +1567,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.91</v>
+        <v>0.903</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Error Monitoring Service</t>
+          <t>Payment Service</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1605,19 +1605,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_04', 'P_01']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1641,7 +1641,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1649,12 +1649,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9159</v>
+        <v>0.9058</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prisma</t>
+          <t>Email Service</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1687,29 +1687,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_05']</t>
+          <t>['AU_04', 'P_01']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Prism</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Prisma as ORM</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1717,13 +1717,13 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1731,12 +1731,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1745,11 +1745,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9391</v>
+        <v>0.9096</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Payment Processing Service</t>
+          <t>Analytics Service</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1769,19 +1769,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_04', 'P_01']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1805,7 +1805,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1813,12 +1813,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M08_AU12</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9431</v>
+        <v>0.9159</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cloud Storage Service</t>
+          <t>Prisma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1851,29 +1851,29 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_04', 'P_05']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Cloud storage</t>
+          <t>Prism</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Cloud storage</t>
+          <t>Prisma as ORM</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1881,13 +1881,13 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M08_AU12</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2083,23 +2083,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>React es una biblioteca de JavaScript de código abierto diseñada para construir interfaces de usuario (UI) de manera eficiente y flexible.</t>
+          <t>System Service (Next.js) sirve la aplicación web mediante React.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_04', 'P_02']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: Data Service (PostgreSQL).</t>
+          <t>Data Service (PostgreSQL) proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
+          <t>En el caso de esta aplicación, dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2427,7 +2427,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2465,31 +2465,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>Data Service (PostgreSQL) proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2499,29 +2503,29 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_08', 'AU_10', 'AU_12', 'AU_14', 'AU_16', 'AU_18']</t>
+          <t>['AU_06', 'P_01']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>system service, authentication service, cloud storage service, payment processing service, analytics service, error monitoring service, email service</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t>Data Service (PostgreSQL)</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2529,30 +2533,26 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
+          <t>CF_M08_AU07</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
-        </is>
-      </c>
+          <t>CF_M08_AU08</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M08_AU08</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2585,19 +2585,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_06']</t>
+          <t>['AU_08']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL)</t>
+          <t>Use Google for user authentication</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2615,13 +2615,13 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M08_AU08</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2629,12 +2629,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Utiliza Google para la autenticación de usuarios.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2667,19 +2667,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_08']</t>
+          <t>['AU_10']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Use Google for user authentication</t>
+          <t>Amazon S3 (for cloud)</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2697,13 +2697,13 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2711,17 +2711,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2729,17 +2729,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
+          <t>It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2749,29 +2749,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_10']</t>
+          <t>['P_01', 'AU_06']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Amazon S3 (for cloud)</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2779,13 +2779,13 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2793,17 +2793,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2811,17 +2811,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2831,29 +2831,29 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_04']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
+          <t>Integrate with Stripe to handle payments and subscriptions</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2861,13 +2861,13 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2875,17 +2875,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2893,63 +2893,55 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Integra con Stripe para manejar pagos y suscripciones.</t>
+          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['AU_12']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Integrate with Stripe to handle payments and subscriptions</t>
+          <t>architecture based on microservices</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>CF_M08_AU13</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2957,12 +2949,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2975,7 +2967,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2985,7 +2977,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: Security Service (Traefik).</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2995,19 +2987,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_02', 'P_01']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3017,17 +3009,21 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
+          <t>Security Service (Traefik)</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CF_M08_AU02</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3035,17 +3031,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3053,55 +3049,63 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>System Service (Next.js) sirve la aplicación web mediante React.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>['P_01']</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>architecture based on microservices</t>
+          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3109,12 +3113,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3127,7 +3131,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3137,29 +3141,29 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Como se puede observar en la figura 6, el Security Service está compuesto exclusivamente por ciertas funcionalidades de la herramienta Traefik.</t>
+          <t>System Service (Next.js) sirve la aplicación web mediante React.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_04', 'P_02']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3169,21 +3173,21 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3191,12 +3195,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3209,49 +3213,49 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>System Service</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: System Service (Next.js).</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_14']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>System Service</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -3259,180 +3263,16 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CF_M08_AU05</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Next.js</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Como se puede observar en la figura 6, el System Service está principalmente desarrollado en Next.js.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>['AU_04']</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Next.js</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>System Service (Next.js)</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>CF_M08_AU04</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>CF_M08_AU05</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CF_M08_AU17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Google Analytics</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>['AU_14']</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Google Analytics</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>CF_M08_AU15</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>CF_M08_AU17</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3529,7 +3369,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3539,69 +3379,69 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.894</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>security service, system service</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
+          <t>Security Service (Traefik) [...] Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3612,32 +3452,28 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>security service, system service</t>
+          <t>system service, data service</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Next.js</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.7444</v>
+        <v>0.8399</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3648,28 +3484,28 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>system service, data service</t>
+          <t>system service, google, amazon s3, stripe, google analytics, sentry, brevo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>System Service (Next.js) [...] Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
+          <t>CF_M08_AU25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.8608</v>
+        <v>0.7479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3685,7 +3521,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Data Service (PostgreSQL) [...] Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3695,13 +3531,13 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.7562</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3712,26 +3548,22 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>system service, system service</t>
+          <t>system service, prisma</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al interactuar con un componente de cliente, este puede acceder al servidor mediante el uso de las server actions.</t>
+          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M08_P06</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.8107</v>
+        <v>0.8399</v>
       </c>
     </row>
   </sheetData>
@@ -3745,7 +3577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3855,39 +3687,111 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.8608</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>CF_M08_AU25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Authentication Service</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8391</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M08_AU23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0.7383</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>CF_M08_P06</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>0.8107</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.714</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6842</v>
+        <v>0.8462</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7222</v>
+        <v>0.9167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9286</v>
+        <v>0.9</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8966</v>
+        <v>0.931</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9552</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="6">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8462</v>
+        <v>0.8571</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8267</v>
+        <v>0.8563</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9615</v>
+        <v>0.8571</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.12</v>
+        <v>0.1481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>0.913</v>
+        <v>0.88</v>
       </c>
       <c r="F2" t="n">
-        <v>0.913</v>
+        <v>0.9565</v>
       </c>
     </row>
     <row r="3">
@@ -670,16 +670,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.8571</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 10</t>
+          <t>7 / 9</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0 / 0</t>
+          <t>6 / 6</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6842</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7222</v>
+        <v>0.9167</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +888,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
         <v>28</v>
-      </c>
-      <c r="D2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G2" t="n">
-        <v>26</v>
-      </c>
-      <c r="H2" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +916,22 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +944,22 @@
         <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -972,22 +972,22 @@
         <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -1000,22 +1000,22 @@
         <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,81 +1165,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7743</v>
+        <v>0.825</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monitoring Service</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_01']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Error monitoring</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M08_AU18</t>
+          <t>CF_M08_P04</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1247,81 +1243,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AU12</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8204</v>
+        <v>0.891</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Storage Service</t>
+          <t>Singleton Pattern</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_01']</t>
+          <t>['P_01', 'AU_10']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Cloud storage</t>
+          <t>Singleton</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Cloud storage</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CF_M08_P01</t>
-        </is>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M08_AU12</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1329,77 +1321,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M08_P04</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.825</v>
+        <v>0.8952</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_04']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers. These observers subscribe to the subject to receive notifications of changes in their status. When the state of the subject changes, it automatically notifies all its observers, allowing them to react appropriately</t>
+          <t>Authentication: Use Google for user authentication.</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M08_P04</t>
+          <t>CF_M08_AU10</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1407,77 +1403,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M08_P05</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.891</v>
+        <v>0.9058</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Singleton Pattern</t>
+          <t>Email Service</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_06']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Singleton</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, records or connections to databases, where having multiple instances could lead to inconsistent states or inefficient use of resources</t>
+          <t>Connects to Brevo to create, send and schedule emails electronics.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M08_P05</t>
+          <t>CF_M08_AU20</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1485,12 +1485,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1499,11 +1499,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8952</v>
+        <v>0.9096</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>Analytics Service</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1523,19 +1523,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_01']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Analytics: Implement Google Analytics to track and analyze the traffic of the site.</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1559,7 +1559,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M08_AU10</t>
+          <t>CF_M08_AU16</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1567,12 +1567,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.903</v>
+        <v>0.91</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Payment Service</t>
+          <t>Error Monitoring Service</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1605,19 +1605,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_01']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>Error monitoring</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Payment processing</t>
+          <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1641,7 +1641,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M08_AU14</t>
+          <t>CF_M08_AU18</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1649,12 +1649,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1663,11 +1663,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9058</v>
+        <v>0.9391</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Email Service</t>
+          <t>Payment Processing Service</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1687,19 +1687,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_01']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Payment processing</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1723,7 +1723,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M08_AU20</t>
+          <t>CF_M08_AU14</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1731,12 +1731,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M08_AU16</t>
+          <t>CF_M08_AU12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1745,11 +1745,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9096</v>
+        <v>0.9431</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Analytics Service</t>
+          <t>Cloud Storage Service</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1769,19 +1769,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_01']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Cloud storage</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1805,7 +1805,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M08_AU16</t>
+          <t>CF_M08_AU12</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1813,81 +1813,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_P03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9159</v>
+        <v>0.9946</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prisma</t>
+          <t>Component-Based</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_05']</t>
+          <t>['P_01', 'AU_05']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Prism</t>
+          <t>Component-based</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Prisma as ORM</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>CF_M08_P02</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_P03</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1895,77 +1891,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M08_P03</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9946</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Component-Based</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components.</t>
+          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: Security Service (Traefik).</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_04']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Component-based</t>
+          <t>Security Service</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components</t>
+          <t>It works as a reverse proxy and load balancer.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CF_M08_P01</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M08_P03</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1973,12 +1973,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1991,63 +1991,63 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>React</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: Security Service (Traefik).</t>
+          <t>React es una biblioteca de JavaScript de código abierto diseñada para construir interfaces de usuario (UI) de manera eficiente y flexible.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_05', 'P_02']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Security Service</t>
+          <t>React</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>It works as a reverse proxy and load balancer. • Manages the routing of HTTP and HTTPS requests towards the Next.js application (System Service). • Exposes ports 80 (HTTP) and 443 (HTTPS) to the outside world and redirects traffic to internal services according to defined rules</t>
+          <t>It serves the web application using React</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>System Service (Next.js) sirve la aplicación web mediante React.</t>
+          <t>Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_02']</t>
+          <t>['AU_21']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -2105,7 +2105,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>It serves the web application using React</t>
+          <t>Connects to Brevo to create, send and schedule emails.</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -2123,13 +2123,13 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU21</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2137,12 +2137,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M08_AU21</t>
+          <t>CF_M08_AU07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2155,49 +2155,49 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brevo</t>
+          <t>Data Service</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: Data Service (PostgreSQL).</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_18']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Brevo</t>
+          <t>Data Service</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Connects to Brevo to create, send and schedule emails.</t>
+          <t>Data Service: • Provides the relational database to store application data.</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2205,13 +2205,13 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M08_AU21</t>
+          <t>CF_M08_AU07</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2219,12 +2219,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
+          <t>Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2257,29 +2257,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_19']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Data Service</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Data Service: • Provides the relational database to store application data. • Communicates directly with Prisma to manage database queries</t>
+          <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -2287,13 +2287,13 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2301,12 +2301,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+          <t>Cabe destacar que cada uno de estos servicios esta contenido en un contenedor de Docker.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2339,19 +2339,19 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_16']</t>
+          <t>['AU_02', 'AU_04', 'AU_06']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Use Sentry to track and manage errors in the application</t>
+          <t>Each of these services is contained in a Docker container</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2369,13 +2369,13 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2383,67 +2383,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>En el caso de esta aplicación, dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_04', 'AU_06']</t>
+          <t>['AU_04', 'AU_11', 'AU_13', 'AU_15', 'AU_17', 'AU_19', 'AU_21']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>system service, authentication service, cloud storage service, payment processing service, analytics service, error monitoring service, email service</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Each of these services is contained in a Docker container</t>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -2451,16 +2447,20 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>CF_M08_AU25</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL)</t>
+          <t>Communicates with the PostgreSQL database service (Data Service) using Prisma as ORM (Object-Relational Mapping).</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2547,7 +2547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios.</t>
+          <t>Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2585,13 +2585,13 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_08']</t>
+          <t>['AU_11']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Use Google for user authentication</t>
+          <t>Authentication: Use Google for user authentication.</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2629,7 +2629,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
+          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2667,13 +2667,13 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_10']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Amazon S3 (for cloud)</t>
+          <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_06']</t>
+          <t>['P_01', 'AU_07']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2793,12 +2793,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2821,29 +2821,29 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2853,21 +2853,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Integrate with Stripe to handle payments and subscriptions</t>
+          <t>HTTPS, which is the standard for secure communications on the web</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>CF_M08_AU13</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2875,17 +2871,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2893,55 +2889,63 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>['AU_15']</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>architecture based on microservices</t>
+          <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CF_M08_AU13</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2949,17 +2953,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2967,17 +2971,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: Security Service (Traefik).</t>
+          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2985,45 +2989,37 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['AU_02', 'P_01']</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t>architecture based on microservices</t>
         </is>
       </c>
       <c r="P24" t="n">
         <v>41</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>CF_M08_AU02</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3031,12 +3027,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3049,63 +3045,63 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>System Service</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>System Service (Next.js) sirve la aplicación web mediante React.</t>
+          <t>Security Service (Traefik) funciona como un proxy inverso y balanceador de carga.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_02', 'P_01']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>System Service</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>It serves the web application using React. • It communicates with the PostgreSQL database service (Data Service) using Prisma as ORM7 (Object-Relational Mapping). • It depends on Traefik to receive and manage HTTP/HTTPS traffic. • Interacts with various external services for specific functionalities</t>
+          <t>Security Service (Traefik)</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU02</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3113,12 +3109,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3131,49 +3127,49 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>System Service (Next.js) sirve la aplicación web mediante React.</t>
+          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: System Service (Next.js).</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_02']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>System Service (Next.js)</t>
+          <t xml:space="preserve">It serves the web application using React. </t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -3181,13 +3177,13 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3195,12 +3191,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3213,7 +3209,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3223,7 +3219,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+          <t>System Service (Next.js) sirve la aplicación web mediante React.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3233,19 +3229,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['AU_14']</t>
+          <t>['AU_04', 'P_02']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3255,7 +3251,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -3263,16 +3259,180 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>CF_M08_AU17</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Google Analytics</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>['AU_17']</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Google Analytics</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CF_M08_AU15</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CF_M08_AU17</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Prisma</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>['AU_04', 'P_05']</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Prisma</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Communicates with the PostgreSQL database service (Data Service) using Prisma as ORM (Object-Relational Mapping).</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CF_M08_P02</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3369,7 +3529,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3379,69 +3539,69 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>security service, system service</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Security Service (Traefik) [...] Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+          <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7383</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3452,28 +3612,32 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>system service, data service</t>
+          <t>security service, system service</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0.8399</v>
+        <v>0.7444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3484,28 +3648,28 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>system service, google, amazon s3, stripe, google analytics, sentry, brevo</t>
+          <t>system service, data service</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>System Service (Next.js) [...] Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.7479</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3516,28 +3680,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>data service, prisma</t>
+          <t>system service, security service</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) [...] Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Depende de Traefik para recibir y gestionar el tráfico HTTP/HTTPS.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Traefik</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>0.8547</v>
+        <v>0.8131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3548,12 +3716,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>system service, prisma</t>
+          <t>data service, prisma</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3563,7 +3731,7 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.8399</v>
+        <v>0.7562</v>
       </c>
     </row>
   </sheetData>
@@ -3577,7 +3745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3646,7 +3814,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3687,29 +3855,29 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.8547</v>
+        <v>0.8608</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_P06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
-        </is>
-      </c>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3719,79 +3887,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Authentication Service</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8391</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CF_M08_AU23</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HTTPS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HTTPS, which is the standard for secure communications on the web</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>0.7383</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CF_M08_P06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.714</v>
+        <v>0.727</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8462</v>
+        <v>0.8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9167</v>
+        <v>0.8889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9</v>
+        <v>0.8966</v>
       </c>
       <c r="C3" t="n">
-        <v>0.931</v>
+        <v>0.8966</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9709</v>
+        <v>0.9697</v>
       </c>
     </row>
     <row r="6">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8571</v>
+        <v>0.7407</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8563</v>
+        <v>0.8415</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8571</v>
+        <v>0.7778</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1481</v>
+        <v>0.2692</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8333</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="4">
@@ -670,13 +670,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6667</v>
+        <v>0.5455</v>
       </c>
       <c r="F4" t="n">
         <v>0.8571</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 9</t>
+          <t>7 / 11</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8462</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9167</v>
+        <v>0.8889</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +888,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="n">
         <v>27</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F2" t="n">
-        <v>27</v>
-      </c>
-      <c r="G2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +916,22 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +944,22 @@
         <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -972,22 +972,22 @@
         <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -1000,22 +1000,22 @@
         <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
         <v>27</v>
-      </c>
-      <c r="F6" t="n">
-        <v>23</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['P_01', 'AU_05']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_10']</t>
+          <t>['P_01', 'AU_07']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1529,7 +1529,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1693,7 +1693,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1775,7 +1775,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_05', 'P_02']</t>
+          <t>['AU_04', 'P_02']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2093,13 +2093,13 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_21']</t>
+          <t>['AU_18']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2257,13 +2257,13 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_19']</t>
+          <t>['AU_16']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2301,7 +2301,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cabe destacar que cada uno de estos servicios esta contenido en un contenedor de Docker.</t>
+          <t>Dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2345,7 +2345,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>System Service (Next.js) interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2417,13 +2417,13 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_11', 'AU_13', 'AU_15', 'AU_17', 'AU_19', 'AU_21']</t>
+          <t>['AU_04', 'AU_08', 'AU_10', 'AU_12', 'AU_14', 'AU_16', 'AU_18']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
+          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_06', 'P_01']</t>
+          <t>['AU_06']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2547,7 +2547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2585,13 +2585,13 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_11']</t>
+          <t>['AU_08']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2667,13 +2667,13 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_10']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -2711,17 +2711,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2729,17 +2729,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine.</t>
+          <t>Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2749,29 +2749,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_07']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
+          <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2779,13 +2779,13 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2821,23 +2821,23 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Traefik abre el puerto 443 para manejar tráfico HTTPS, que es el estándar para comunicaciones seguras en la web.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2871,17 +2871,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2889,63 +2889,55 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Integra con Stripe para manejar pagos y suscripciones.</t>
+          <t>The architecture of software based on microservices is a design and software development approach where an application is built as a collection of small and independent services that communicate with each other.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['AU_15']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
+          <t>architecture based on microservices</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>CF_M08_AU13</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2953,17 +2945,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2971,55 +2963,63 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Traefik es un proxy inverso y balanceador de carga moderno diseñado para gestionar la entrada y salida de tráfico HTTP y HTTPS en aplicaciones basadas en contenedores.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>['AU_02']</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>architecture based on microservices</t>
+          <t>Security Service (Traefik)</t>
         </is>
       </c>
       <c r="P24" t="n">
         <v>41</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CF_M08_AU02</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3027,12 +3027,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Security Service (Traefik) funciona como un proxy inverso y balanceador de carga.</t>
+          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: System Service (Next.js).</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3065,43 +3065,43 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['AU_02', 'P_01']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Security Service (Traefik)</t>
+          <t xml:space="preserve">It serves the web application using React. </t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CF_M08_AU02</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3109,12 +3109,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3127,49 +3127,49 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>System Service</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Como se puede observar en la figura 6, los tres servicios principales de la aplicación son: System Service (Next.js).</t>
+          <t>Next.js es un framework para la creación de aplicaciones web que ofrece una estructura adicional, características y optimizaciones que permiten construir aplicaciones más rápido.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>System Service</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">It serves the web application using React. </t>
+          <t>System Service (Next.js)</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -3177,13 +3177,13 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3191,12 +3191,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>System Service (Next.js) sirve la aplicación web mediante React.</t>
+          <t>Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3229,19 +3229,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_02']</t>
+          <t>['AU_14']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Google Analytics</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>System Service (Next.js)</t>
+          <t>Implement Google Analytics to track and analyze site traffic</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -3259,13 +3259,13 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M08_AU04</t>
+          <t>CF_M08_AU15</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3273,12 +3273,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Prisma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['AU_17']</t>
+          <t>['AU_04', 'P_04']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Google Analytics</t>
+          <t>Prisma</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Implement Google Analytics to track and analyze site traffic</t>
+          <t>Communicates with the PostgreSQL database service (Data Service) using Prisma as ORM (Object-Relational Mapping).</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -3341,98 +3341,16 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CF_M08_AU15</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CF_M08_AU09</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Prisma</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>['AU_04', 'P_05']</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Prisma</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Communicates with the PostgreSQL database service (Data Service) using Prisma as ORM (Object-Relational Mapping).</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>CF_M08_P02</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>CF_M08_AU09</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3529,7 +3447,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3545,7 +3463,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js.</t>
+          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3617,21 +3535,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
+          <t>Traefik gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service).</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7444</v>
+        <v>0.7524</v>
       </c>
     </row>
     <row r="6">
@@ -3653,7 +3571,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
+          <t>System Service (Next.js) se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3663,13 +3581,13 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.8608</v>
+        <v>0.8296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3680,26 +3598,22 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>system service, security service</t>
+          <t>data service, prisma</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Depende de Traefik para recibir y gestionar el tráfico HTTP/HTTPS.</t>
+          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Traefik</t>
-        </is>
-      </c>
+          <t>CF_M08_AU24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.8131</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="8">
@@ -3716,22 +3630,26 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>data service, prisma</t>
+          <t>security service, http, https</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro [...] Traefik abre el puerto 443 para manejar tráfico HTTPS.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M08_AU23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HTTPS</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>0.7562</v>
+        <v>0.756</v>
       </c>
     </row>
   </sheetData>
@@ -3745,7 +3663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3814,7 +3732,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3850,47 +3768,79 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.8608</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_P06</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.673</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M08_P06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>0.727</v>
       </c>
     </row>

--- a/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M08_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8889</v>
+        <v>0.9167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8966</v>
+        <v>0.9</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8966</v>
+        <v>0.931</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9697</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="6">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7407</v>
+        <v>0.8148</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8415</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7778</v>
+        <v>0.8889</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2692</v>
+        <v>0.2308</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fixes</t>
+          <t>fixedType</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -648,16 +648,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6667</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="4">
@@ -670,13 +670,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5455</v>
+        <v>0.75</v>
       </c>
       <c r="F4" t="n">
         <v>0.8571</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 11</t>
+          <t>7 / 8</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8</v>
+        <v>0.8683999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8889</v>
+        <v>0.9167</v>
       </c>
     </row>
     <row r="12">
@@ -888,19 +888,19 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
         <v>27</v>
@@ -916,7 +916,7 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
         <v>27</v>
@@ -944,7 +944,7 @@
         <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
         <v>27</v>
@@ -956,7 +956,7 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
         <v>27</v>
@@ -972,7 +972,7 @@
         <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
         <v>27</v>
@@ -984,7 +984,7 @@
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
         <v>27</v>
@@ -1000,7 +1000,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
         <v>22</v>
@@ -1012,7 +1012,7 @@
         <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>27</v>
@@ -1021,7 +1021,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fixes</t>
+          <t>fixedType</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>LLM_fixes</t>
+          <t>LLM_fixedType</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>GT_fixes</t>
+          <t>GT_fixedType</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where an object known as the subject maintains a list of other objects called observers.</t>
+          <t>El patrón Observer establece una relación de uno a muchos entre objetos, donde un objeto conocido como el sujeto mantiene una lista de otros objetos llamados observadores.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_05']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance.</t>
+          <t>El patrón Singleton asegura que una clase tenga solo una instancia y proporciona un punto de acceso global a esa instancia.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_07']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1529,7 +1529,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1693,7 +1693,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1775,7 +1775,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components.</t>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['P_01', 'AU_05']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1973,7 +1973,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>React es una biblioteca de JavaScript de código abierto diseñada para construir interfaces de usuario (UI) de manera eficiente y flexible.</t>
+          <t>React es una biblioteca de JavaScript de código abierto diseñada para construir interfaces de usuario.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2017,7 +2017,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2093,13 +2093,13 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_18']</t>
+          <t>['AU_20']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>41, 42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2219,12 +2219,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+          <t>Cabe destacar que cada uno de estos servicios esta contenido en un contenedor de Docker.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2257,19 +2257,19 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_16']</t>
+          <t>['AU_02', 'AU_04', 'AU_06']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
+          <t>Each of these services is contained in a Docker container</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -2287,13 +2287,13 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M08_AU17</t>
+          <t>CF_M08_P01</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M08_AU19</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2301,12 +2301,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2329,29 +2329,29 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
+          <t>Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_04', 'AU_06']</t>
+          <t>['AU_18']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Each of these services is contained in a Docker container</t>
+          <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2369,13 +2369,13 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M08_P01</t>
+          <t>CF_M08_AU17</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU19</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2383,31 +2383,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
+          <t>CF_M08_AU08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>System Service (Next.js) interactúa con varios servicios externos para funcionalidades específicas: Autenticación: Utiliza Google para la autenticación de usuarios. [...] Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. [...] Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. [...] Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. [...] Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. [...] Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2417,29 +2421,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_08', 'AU_10', 'AU_12', 'AU_14', 'AU_16', 'AU_18']</t>
+          <t>['AU_06']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>system service, authentication service, cloud storage service, payment processing service, analytics service, error monitoring service, email service</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
+          <t>Communicates with the PostgreSQL database service (Data Service) using Prisma as ORM (Object-Relational Mapping).</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -2447,30 +2451,26 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M08_AU04, CF_M08_AU10, CF_M08_AU12, CF_M08_AU14, CF_M08_AU16, CF_M08_AU18, CF_M08_AU20</t>
+          <t>CF_M08_AU07</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M08_AU25</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
-        </is>
-      </c>
+          <t>CF_M08_AU08</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M08_AU08</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación.</t>
+          <t>Utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2503,19 +2503,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_06']</t>
+          <t>['AU_10']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Communicates with the PostgreSQL database service (Data Service) using Prisma as ORM (Object-Relational Mapping).</t>
+          <t>Authentication: Use Google for user authentication.</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2533,13 +2533,13 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M08_AU07</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M08_AU08</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2547,12 +2547,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Utiliza Google para la autenticación de usuarios.</t>
+          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2585,19 +2585,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_08']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Authentication: Use Google for user authentication.</t>
+          <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2615,13 +2615,13 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU11</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2629,17 +2629,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2647,17 +2647,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM (Object-Relational Mapping).</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2667,29 +2667,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_10']</t>
+          <t>['P_01', 'AU_09']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
+          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2697,13 +2697,13 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M08_AU11</t>
+          <t>CF_M08_AU04</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M08_AU13</t>
+          <t>CF_M08_P02</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2711,7 +2711,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2749,13 +2749,13 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_14']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Traefik abre el puerto 443 para manejar tráfico HTTPS, que es el estándar para comunicaciones seguras en la web.</t>
+          <t>Traefik abre el puerto 443 para manejar tráfico HTTPS.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2831,13 +2831,13 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_02', 'AU_26']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>The architecture of software based on microservices is a design and software development approach where an application is built as a collection of small and independent services that communicate with each other.</t>
+          <t>La arquitectura de software basada en microservicios es un enfoque de diseño y desarrollo de software donde una aplicación se construye como una colección de servicios pequeños e independientes que se comunican entre sí.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Traefik es un proxy inverso y balanceador de carga moderno diseñado para gestionar la entrada y salida de tráfico HTTP y HTTPS en aplicaciones basadas en contenedores.</t>
+          <t>El Security Service está compuesto exclusivamente por ciertas funcionalidades de la herramienta Traefik.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>41, 42</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Next.js es un framework para la creación de aplicaciones web que ofrece una estructura adicional, características y optimizaciones que permiten construir aplicaciones más rápido.</t>
+          <t>El System Service está principalmente desarrollado en Next.js.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3191,7 +3191,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3229,13 +3229,13 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['AU_14']</t>
+          <t>['AU_16']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3273,7 +3273,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3311,13 +3311,13 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_04']</t>
+          <t>['AU_04', 'P_05', 'AU_27']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3363,7 +3363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3447,7 +3447,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3463,7 +3463,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro.</t>
+          <t>Traefik abre el puerto 80 para manejar tráfico HTTP.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3483,7 +3483,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3598,28 +3598,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>data service, prisma</t>
+          <t>system service, authentication service</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Service (PostgreSQL) se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+          <t>System Service (Next.js) utiliza Google para la autenticación de usuarios.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M08_AU24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>0.8529</v>
+        <v>0.7514</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3630,26 +3634,170 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>security service, http, https</t>
+          <t>system service, cloud storage service</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Traefik abre el puerto 80 para manejar tráfico HTTP no seguro [...] Traefik abre el puerto 443 para manejar tráfico HTTPS.</t>
+          <t>System Service (Next.js) utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M08_AU23</t>
+          <t>CF_M08_AU13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HTTPS</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.756</v>
+        <v>0.7913</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>system service, payment processing service</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) integra con Stripe para manejar pagos y suscripciones.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7436</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>system service, analytics service</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M08_AU17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Google Analytics</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7814</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>system service, error monitoring service</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7448</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AU_33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>system service, email service</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>System Service (Next.js) se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M08_AU05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Next.js</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7239</v>
       </c>
     </row>
   </sheetData>
@@ -3732,7 +3880,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3768,44 +3916,52 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>0.8529</v>
+        <v>0.8507</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_P02</t>
+          <t>CF_M08_AU25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
+          <t>• Interacts with various external services for specific functionalities [...] Authentication</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Authentication Service</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.673</v>
+        <v>0.8391</v>
       </c>
     </row>
     <row r="5">
@@ -3832,7 +3988,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
